--- a/product_selector_out/STM32F105-107.xlsx
+++ b/product_selector_out/STM32F105-107.xlsx
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AL12" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM12" s="4" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM13" s="4" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AL14" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM14" s="4" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM15" s="4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AL16" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM16" s="4" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AL17" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM17" s="4" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AL18" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM18" s="4" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM19" s="4" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AL20" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM20" s="4" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="AL21" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM21" s="4" t="inlineStr">
@@ -4949,14 +4949,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="8" t="inlineStr">
@@ -4979,9 +4979,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="8" t="inlineStr">
@@ -5034,9 +5034,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM12" s="6" t="inlineStr">
@@ -5276,14 +5276,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="8" t="inlineStr">
@@ -5306,9 +5306,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr">
@@ -5361,9 +5361,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM13" s="6" t="inlineStr">
@@ -5603,14 +5603,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
@@ -5633,9 +5633,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="8" t="inlineStr">
@@ -5688,9 +5688,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM14" s="6" t="inlineStr">
@@ -5930,14 +5930,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
@@ -5960,9 +5960,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="8" t="inlineStr">
@@ -6015,9 +6015,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM15" s="6" t="inlineStr">
@@ -6257,14 +6257,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="8" t="inlineStr">
@@ -6287,9 +6287,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="8" t="inlineStr">
@@ -6342,9 +6342,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM16" s="6" t="inlineStr">
@@ -6584,14 +6584,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
@@ -6614,9 +6614,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="8" t="inlineStr">
@@ -6669,9 +6669,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM17" s="6" t="inlineStr">
@@ -6911,14 +6911,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W18" s="8" t="inlineStr">
@@ -6941,9 +6941,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -6996,9 +6996,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -7238,14 +7238,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
@@ -7268,9 +7268,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="8" t="inlineStr">
@@ -7323,9 +7323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -7565,14 +7565,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
@@ -7595,9 +7595,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="8" t="inlineStr">
@@ -7650,9 +7650,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -7892,14 +7892,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
@@ -7922,9 +7922,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="8" t="inlineStr">
@@ -7977,9 +7977,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8182,14 +8182,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32F105VB</t>
+          <t>STM32F105VC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8211,12 +8211,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32F107RB</t>
+          <t>STM32F105VB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8226,14 +8226,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32F107RC</t>
+          <t>STM32F105VB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8255,12 +8255,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32F107VB</t>
+          <t>STM32F107RB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8270,14 +8270,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32F105R8</t>
+          <t>STM32F107RB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8299,12 +8299,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32F105RB</t>
+          <t>STM32F107RC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32F105RC</t>
+          <t>STM32F107RC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8343,12 +8343,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F105V8</t>
+          <t>STM32F107VB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8358,27 +8358,247 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>STM32F107VB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32F105R8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32F105R8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32F105RB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32F105RB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32F105RC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32F105RC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32F105V8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32F105V8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>STM32F107VC</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>summary row reads USART = 5 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32F107VC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Operating Temperature (°C) max</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Ambient temperatures: –40 to +85 °C /–40 to +105 °C Junction temperature: –40 to + 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32F105-107.xlsx
+++ b/product_selector_out/STM32F105-107.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM21"/>
+  <dimension ref="A1:BN21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.40625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
@@ -4257,12 +4309,17 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f105r8.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -4283,16 +4340,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -4305,6 +4360,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -4324,7 +4380,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -4351,7 +4409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM21"/>
+  <dimension ref="A1:BN21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4419,6 +4477,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4752,6 +4811,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4847,6 +4911,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5169,7 +5234,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5496,7 +5566,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5823,7 +5898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6150,7 +6230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6477,7 +6562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6804,7 +6894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7131,7 +7226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7458,7 +7558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7785,7 +7890,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8112,7 +8222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8120,8 +8235,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
